--- a/reports/CredPilot_Internal_Peer_Review.xlsx
+++ b/reports/CredPilot_Internal_Peer_Review.xlsx
@@ -602,7 +602,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 15:24:35</t>
+          <t>2026-09-22 16:04:23</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22T15:24:26Z</t>
+          <t>2026-09-22T16:04:01Z</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -750,7 +750,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>REQ-008, REQ-009, REQ-010, REQ-011, REQ-012, REQ-013, REQ-035, REQ-045, REQ-046</t>
+          <t>REQ-010, REQ-011, REQ-012, REQ-013, REQ-035, REQ-045, REQ-046</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>103/112 requirements, 98% weighted fit, against this repository's own 112-requirement validator.</t>
+          <t>105/112 requirements, 98% weighted fit, against this repository's own 112-requirement validator.</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1387,12 +1387,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>REQ-008</t>
+          <t>REQ-010</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Duration | 20 hours</t>
+          <t>Evaluation Mode | Automated review of the submitted Git repository against the Hackathon Rubric (7 categories / 100 marks), scored entirely from committed evidence in the repository. No live demo judging.</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1401,38 +1401,38 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>0/1 bound tests pass</t>
+          <t>1/2 bound tests pass</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Attestation for REQ-008-T01 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
+          <t>Attestation for REQ-010-T02 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Krishna Annavaram; Mahesh Rajendra</t>
+          <t>External evaluator</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Both members sign docs/team/WORKLOG.md, then populate REQ-008-T01.</t>
+          <t>Official rubric review must be carried out by the evaluator.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>REQ-009</t>
+          <t>REQ-011</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Format | Team of 2–4</t>
+          <t>Submission | Push the final repository to your assigned Virtusa GitLab project by the cut-off.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1441,38 +1441,38 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>0/1 bound tests pass</t>
+          <t>1/3 bound tests pass</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Attestation for REQ-009-T01 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
+          <t>No configured remote names GitLab, but the submission instruction names a Virtusa GitLab project. Remotes found: origin git@github.com:KrishnaAnnavaram/CredPilot.git (fetch) origin; UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'the submission cut-off date and time, and the identity of the assigned Virtusa GitLab projec</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Krishna Annavaram; Mahesh Rajendra</t>
+          <t>Krishna Annavaram</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Both members sign docs/team/TEAM_ATTESTATION.md, then populate REQ-009-T01.</t>
+          <t>Push final commit to the assigned Virtusa GitLab from the Virtusa laptop (T02). T03 is a source gap and cannot close.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>REQ-010</t>
+          <t>REQ-012</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Evaluation Mode | Automated review of the submitted Git repository against the Hackathon Rubric (7 categories / 100 marks), scored entirely from committed evidence in the repository. No live demo judging.</t>
+          <t>Review Output | Per-team Excel report (Summary, Categories, Scorecard, Detailed, Improvement).</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1481,16 +1481,16 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>1/2 bound tests pass</t>
+          <t>0/1 bound tests pass</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Attestation for REQ-010-T02 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
+          <t>Attestation for REQ-012-T01 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,19 +1500,19 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Official rubric review must be carried out by the evaluator.</t>
+          <t>Reviewer produces the per-team Excel report. This workbook is internal preparation, not that report.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>REQ-011</t>
+          <t>REQ-013</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Submission | Push the final repository to your assigned Virtusa GitLab project by the cut-off.</t>
+          <t>Grade Bands | Pass ≥ 60 · Not Yet Passed &lt; 60</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1521,38 +1521,38 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>1/3 bound tests pass</t>
+          <t>0/1 bound tests pass</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>No configured remote names GitLab, but the submission instruction names a Virtusa GitLab project. Remotes found: origin git@github.com:KrishnaAnnavaram/CredPilot.git (fetch) origin; UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'the submission cut-off date and time, and the identity of the assigned Virtusa GitLab projec</t>
+          <t>Attestation for REQ-013-T01 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Krishna Annavaram</t>
+          <t>External evaluator</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Push final commit to the assigned Virtusa GitLab from the Virtusa laptop (T02). T03 is a source gap and cannot close.</t>
+          <t>Grade issued and bands applied by the evaluator.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>REQ-012</t>
+          <t>REQ-035</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Review Output | Per-team Excel report (Summary, Categories, Scorecard, Detailed, Improvement).</t>
+          <t>Language / Agent Framework | Python 3.11+ · LangGraph (MIT)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1561,38 +1561,38 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>0/1 bound tests pass</t>
+          <t>2/3 bound tests pass</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Attestation for REQ-012-T01 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
+          <t>UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'any licence artifact the implementation must carry to evidence LangGraph's MIT licence' coul</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>External evaluator</t>
+          <t>N/A - source specification gap</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Reviewer produces the per-team Excel report. This workbook is internal preparation, not that report.</t>
+          <t>Third-party licence evidence added (docs/THIRD_PARTY_LICENSES.md). The source requires no licence artifact, so the check cannot pass.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>REQ-013</t>
+          <t>REQ-045</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Grade Bands | Pass ≥ 60 · Not Yet Passed &lt; 60</t>
+          <t>AC-02 | The copilot computes affordability (DTI / disposable income) from the application data and flags any policy breach with the threshold it failed.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1601,38 +1601,38 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>0/1 bound tests pass</t>
+          <t>3/4 bound tests pass</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Attestation for REQ-013-T01 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
+          <t>UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'the numeric DTI or disposable-income threshold that constitutes a policy breach' could be ve</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>External evaluator</t>
+          <t>N/A - source specification gap</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Grade issued and bands applied by the evaluator.</t>
+          <t>Thresholds come from the retrieved policy corpus. The source states no DTI number; do not hard-code one.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>REQ-035</t>
+          <t>REQ-046</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Language / Agent Framework | Python 3.11+ · LangGraph (MIT)</t>
+          <t>AC-03 | The copilot produces a decision recommendation (approve / refer / decline) with a written rationale; a decline or high-value case is routed for human review rather than auto-decided.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2/3 bound tests pass</t>
+          <t>6/7 bound tests pass</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'any licence artifact the implementation must carry to evidence LangGraph's MIT licence' coul</t>
+          <t xml:space="preserve">UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'the loan value above which a case counts as a high-value case' could be verified against an </t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1660,89 +1660,43 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Third-party licence evidence added (docs/THIRD_PARTY_LICENSES.md). The source requires no licence artifact, so the check cannot pass.</t>
+          <t>High-value routing keys off the policy corpus. The source states no monetary boundary; do not invent one.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>REQ-045</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>AC-02 | The copilot computes affordability (DTI / disposable income) from the application data and flags any policy breach with the threshold it failed.</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>3/4 bound tests pass</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'the numeric DTI or disposable-income threshold that constitutes a policy breach' could be ve</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>N/A - source specification gap</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Thresholds come from the retrieved policy corpus. The source states no DTI number; do not hard-code one.</t>
-        </is>
-      </c>
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr"/>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>REQ-046</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>PASSING</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>AC-03 | The copilot produces a decision recommendation (approve / refer / decline) with a written rationale; a decline or high-value case is routed for human review rather than auto-decided.</t>
+          <t>105 of 112 requirements pass and are not itemised here. Full detail: requirements_validation_tests/reports/latest_test_report.md</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>6/7 bound tests pass</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'the loan value above which a case counts as a high-value case' could be verified against an </t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>N/A - source specification gap</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>High-value routing keys off the policy corpus. The source states no monetary boundary; do not invent one.</t>
-        </is>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr"/>
@@ -1757,54 +1711,20 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>PASSING</t>
+          <t>NOTE</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>103 of 112 requirements pass and are not itemised here. Full detail: requirements_validation_tests/reports/latest_test_report.md</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>98</v>
-      </c>
+          <t>Internal validator statuses only. No official marks are assigned - the official rubric is not present and has not been run.</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Internal validator statuses only. No official marks are assigned - the official rubric is not present and has not been run.</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1820,7 +1740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1873,12 +1793,12 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>REQ-008</t>
+          <t>REQ-010</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>REQ-008-T01</t>
+          <t>REQ-010-T01</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1888,12 +1808,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Attestation for REQ-008-T01 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
+          <t>E:\Virtusa Projects\CredPilot is a Git repository; git ls-files reports 1883 tracked files</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr"/>
@@ -1901,12 +1821,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>REQ-009</t>
+          <t>REQ-010</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>REQ-009-T01</t>
+          <t>REQ-010-T02</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1921,7 +1841,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Attestation for REQ-009-T01 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
+          <t>Attestation for REQ-010-T02 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
@@ -1929,12 +1849,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>REQ-010</t>
+          <t>REQ-011</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>REQ-010-T01</t>
+          <t>REQ-011-T01</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1949,7 +1869,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>E:\Virtusa Projects\CredPilot is a Git repository; git ls-files reports 1881 tracked files</t>
+          <t>git remote -v: origin git@github.com:KrishnaAnnavaram/CredPilot.git (fetch) origin git@github.com:KrishnaAnnavaram/CredPilot.git (push)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr"/>
@@ -1957,12 +1877,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>REQ-010</t>
+          <t>REQ-011</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>REQ-010-T02</t>
+          <t>REQ-011-T02</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1977,7 +1897,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Attestation for REQ-010-T02 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
+          <t>No configured remote names GitLab, but the submission instruction names a Virtusa GitLab project. Remotes found: origin git@github.com:KrishnaAnnavaram/CredPilot.git (fetch) origin git@github.com:KrishnaAnnavaram/CredPilot.git (push)</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr"/>
@@ -1990,7 +1910,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>REQ-011-T01</t>
+          <t>REQ-011-T03</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -2000,12 +1920,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>git remote -v: origin git@github.com:KrishnaAnnavaram/CredPilot.git (fetch) origin git@github.com:KrishnaAnnavaram/CredPilot.git (push)</t>
+          <t>UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'the submission cut-off date and time, and the identity of the assigned Virtusa GitLab project' could be verified against an implementation.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr"/>
@@ -2013,12 +1933,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>REQ-011</t>
+          <t>REQ-012</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>REQ-011-T02</t>
+          <t>REQ-012-T01</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -2033,7 +1953,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>No configured remote names GitLab, but the submission instruction names a Virtusa GitLab project. Remotes found: origin git@github.com:KrishnaAnnavaram/CredPilot.git (fetch) origin git@github.com:KrishnaAnnavaram/CredPilot.git (push)</t>
+          <t>Attestation for REQ-012-T01 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
@@ -2041,12 +1961,12 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>REQ-011</t>
+          <t>REQ-013</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>REQ-011-T03</t>
+          <t>REQ-013-T01</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -2061,7 +1981,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'the submission cut-off date and time, and the identity of the assigned Virtusa GitLab project' could be verified against an implementation.</t>
+          <t>Attestation for REQ-013-T01 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr"/>
@@ -2069,27 +1989,27 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>REQ-012</t>
+          <t>REQ-035</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>REQ-012-T01</t>
+          <t>REQ-035-T01</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Attestation for REQ-012-T01 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
+          <t>Python &gt;= 3.11 declared at pyproject.toml:5: requires-python = "&gt;=3.11"</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr"/>
@@ -2097,27 +2017,27 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>REQ-013</t>
+          <t>REQ-035</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>REQ-013-T01</t>
+          <t>REQ-035-T02</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>governance</t>
+          <t>integration</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Attestation for REQ-013-T01 is incomplete (evidence='', attested_by='', attested_on='') -&gt; FAIL</t>
+          <t>LangGraph agent framework (ALL: 2/2 satisfied) [OK] langgraph declared (dependency manifests) (ALL: 1/1 satisfied) [OK] requirements.txt:16: langgraph==1.2.11 [OK] langgraph imported (import analysis) (ALL: 1/1 satisfied) [OK] src/graph.py:2441: from langgraph.checkpoint.sqlite import ...</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
@@ -2130,7 +2050,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>REQ-035-T01</t>
+          <t>REQ-035-T03</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -2140,12 +2060,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Python &gt;= 3.11 declared at pyproject.toml:5: requires-python = "&gt;=3.11"</t>
+          <t>UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'any licence artifact the implementation must carry to evidence LangGraph's MIT licence' could be verified against an implementation.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
@@ -2153,17 +2073,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>REQ-035</t>
+          <t>REQ-045</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>REQ-035-T02</t>
+          <t>REQ-045-T01</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>affordability</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -2173,7 +2093,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>LangGraph agent framework (ALL: 2/2 satisfied) [OK] langgraph declared (dependency manifests) (ALL: 1/1 satisfied) [OK] requirements.txt:16: langgraph==1.2.11 [OK] langgraph imported (import analysis) (ALL: 1/1 satisfied) [OK] src/graph.py:2441: from langgraph.checkpoint.sqlite import ...</t>
+          <t>DTI / disposable-income computation across implementation tree (157 files) (ALL: 1/1 satisfied) [OK] eval/agent/dataset.py:320: "DTI-CONV": "src/rules.py — affordability ceiling, with the compensating-factor extension",</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr"/>
@@ -2181,27 +2101,27 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>REQ-035</t>
+          <t>REQ-045</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>REQ-035-T03</t>
+          <t>REQ-045-T02</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>integration</t>
+          <t>affordability</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'any licence artifact the implementation must carry to evidence LangGraph's MIT licence' could be verified against an implementation.</t>
+          <t>affordability figure in observable output (from 'python -m src.cli assess synthetic_data/mortgage/applications/APP-000056.json') (ALL: 1/1 satisfied) [OK] /afford|\bDTI\b|disposable/ matched observable output: 'afford' --- observable output (last lines) --- Policy evidence (61 chunks, 61 distinct citations, all resolve: True) POL-AST-001 v1.0 POL-AST-002 v1.0 POL-AST-002 v1.0 rule AST-FTC-001 POL-</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr"/>
@@ -2214,7 +2134,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>REQ-045-T01</t>
+          <t>REQ-045-T03</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -2229,7 +2149,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>DTI / disposable-income computation across implementation tree (156 files) (ALL: 1/1 satisfied) [OK] eval/agent/dataset.py:320: "DTI-CONV": "src/rules.py — affordability ceiling, with the compensating-factor extension",</t>
+          <t>threshold-bearing policy breach flag across implementation tree (157 files) (ALL: 2/2 satisfied) [OK] eval/agent/dataset.py:316: #: reader, but no code compares them against a threshold. [OK] eval/agent/dataset.py:158: asked, and scoring against it would penalise the system for failing to</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
@@ -2242,7 +2162,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>REQ-045-T02</t>
+          <t>REQ-045-T04</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2252,12 +2172,12 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>affordability figure in observable output (from 'python -m src.cli assess synthetic_data/mortgage/applications/APP-000056.json') (ALL: 1/1 satisfied) [OK] /afford|\bDTI\b|disposable/ matched observable output: 'afford' --- observable output (last lines) --- Policy evidence (61 chunks, 61 distinct citations, all resolve: True) POL-AST-001 v1.0 POL-AST-002 v1.0 POL-AST-002 v1.0 rule AST-FTC-001 POL-</t>
+          <t>UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'the numeric DTI or disposable-income threshold that constitutes a policy breach' could be verified against an implementation.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr"/>
@@ -2265,17 +2185,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>REQ-045</t>
+          <t>REQ-046</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>REQ-045-T03</t>
+          <t>REQ-046-T01</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>affordability</t>
+          <t>underwriting</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -2285,7 +2205,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>threshold-bearing policy breach flag across implementation tree (156 files) (ALL: 2/2 satisfied) [OK] eval/agent/dataset.py:316: #: reader, but no code compares them against a threshold. [OK] eval/agent/dataset.py:158: asked, and scoring against it would penalise the system for failing to</t>
+          <t>Decision vocabulary present in observable output: ['decline'] (from 'python -m src.cli assess synthetic_data/mortgage/applications/APP-000056.json')</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr"/>
@@ -2293,27 +2213,27 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>REQ-045</t>
+          <t>REQ-046</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>REQ-045-T04</t>
+          <t>REQ-046-T02</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>affordability</t>
+          <t>underwriting</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'the numeric DTI or disposable-income threshold that constitutes a policy breach' could be verified against an implementation.</t>
+          <t>the approve / refer / decline outcomes across implementation tree (157 files) (ALL: 3/3 satisfied) [OK] eval/agent/dataset.py:41: #: ``APPROVE_WITH_CONDITIONS`` is listed because the golden sets use it — six [OK] eval/agent/dataset.py:43: #: :func:`src.graph.recommendation_node`, which emits approve, refer or decline [OK] eval/agent/dataset.py:43: #: :func:`src.graph.recommendation_node`, which em</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -2326,7 +2246,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>REQ-046-T01</t>
+          <t>REQ-046-T03</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2341,7 +2261,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Decision vocabulary present in observable output: ['decline'] (from 'python -m src.cli assess synthetic_data/mortgage/applications/APP-000056.json')</t>
+          <t>written rationale in observable output (from 'python -m src.cli assess synthetic_data/mortgage/applications/APP-000056.json') (ALL: 1/1 satisfied) [OK] /rationale|reason|justification|because|explanation/ matched observable output: 'Rationale' --- observable output (last lines) --- Policy evidence (61 chunks, 61 distinct citations, all resolve: True) POL-AST-001 v1.0 POL-AST-002 v1.0 POL-AST-002 v</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr"/>
@@ -2354,7 +2274,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>REQ-046-T02</t>
+          <t>REQ-046-T04</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2369,7 +2289,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>the approve / refer / decline outcomes across implementation tree (156 files) (ALL: 3/3 satisfied) [OK] eval/agent/dataset.py:41: #: ``APPROVE_WITH_CONDITIONS`` is listed because the golden sets use it — six [OK] eval/agent/dataset.py:43: #: :func:`src.graph.recommendation_node`, which emits approve, refer or decline [OK] eval/agent/dataset.py:43: #: :func:`src.graph.recommendation_node`, which em</t>
+          <t>decline handling across implementation tree (157 files) (ALL: 1/1 satisfied) [OK] eval/agent/dataset.py:43: #: :func:`src.graph.recommendation_node`, which emits approve, refer or decline</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
@@ -2382,7 +2302,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>REQ-046-T03</t>
+          <t>REQ-046-T05</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2397,7 +2317,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>written rationale in observable output (from 'python -m src.cli assess synthetic_data/mortgage/applications/APP-000056.json') (ALL: 1/1 satisfied) [OK] /rationale|reason|justification|because|explanation/ matched observable output: 'Rationale' --- observable output (last lines) --- Policy evidence (61 chunks, 61 distinct citations, all resolve: True) POL-AST-001 v1.0 POL-AST-002 v1.0 POL-AST-002 v</t>
+          <t>high-value case routing across implementation tree (157 files) (ALL: 1/1 satisfied) [OK] scripts/build_peer_review_workbook.py:128: "High-value routing keys off the policy corpus. The source states no "</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
@@ -2410,7 +2330,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>REQ-046-T04</t>
+          <t>REQ-046-T06</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2425,7 +2345,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>decline handling across implementation tree (156 files) (ALL: 1/1 satisfied) [OK] eval/agent/dataset.py:43: #: :func:`src.graph.recommendation_node`, which emits approve, refer or decline</t>
+          <t>human-review route across implementation tree (157 files) (ALL: 1/1 satisfied) [OK] eval/agent/dataset.py:63: "PENDING_HUMAN_REVIEW": REFER,</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
@@ -2438,7 +2358,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>REQ-046-T05</t>
+          <t>REQ-046-T07</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2448,95 +2368,39 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>high-value case routing across implementation tree (156 files) (ALL: 1/1 satisfied) [OK] scripts/build_peer_review_workbook.py:128: "High-value routing keys off the policy corpus. The source states no "</t>
+          <t>UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'the loan value above which a case counts as a high-value case' could be verified against an implementation.</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>REQ-046</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>REQ-046-T06</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>underwriting</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>human-review route across implementation tree (156 files) (ALL: 1/1 satisfied) [OK] eval/agent/dataset.py:63: "PENDING_HUMAN_REVIEW": REFER,</t>
-        </is>
-      </c>
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr"/>
+      <c r="D24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>REQ-046</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>REQ-046-T07</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>underwriting</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>NOTE</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>UNSPECIFIED_BY_REQUIREMENT: the source document states no value or artifact from which 'the loan value above which a case counts as a high-value case' could be verified against an implementation.</t>
+          <t>Reviewer notes are intentionally empty. Mahesh Rajendra completes them when the review is performed; no approval text is generated on his behalf.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr"/>
-      <c r="B26" s="4" t="inlineStr"/>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>NOTE</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr"/>
-      <c r="C27" s="4" t="inlineStr"/>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>Reviewer notes are intentionally empty. Mahesh Rajendra completes them when the review is performed; no approval text is generated on his behalf.</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2552,7 +2416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2668,12 +2532,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Both members sign docs/team/TEAM_ATTESTATION.md, then populate REQ-009-T01</t>
+          <t>Team-size attestation signed by both members (REQ-009)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>REQ-009. Team size is an event fact no artifact can establish.</t>
+          <t>Signed 2026-09-22. docs/team/TEAM_ATTESTATION.md; recorded in manual_attestations.json. REQ-009 now PASSES.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -2683,12 +2547,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>PENDING SIGNATURE</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Both members confirming</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2698,12 +2562,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Both members sign docs/team/WORKLOG.md, then populate REQ-008-T01</t>
+          <t>Engagement-duration attestation signed by both members (REQ-008)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>REQ-008. Exact task-level hours are not mechanically derivable from Git.</t>
+          <t>Signed 2026-09-22. docs/team/WORKLOG.md and reports/team_worklog.xlsx; recorded in manual_attestations.json. REQ-008 now PASSES.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2713,12 +2577,12 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>PENDING SIGNATURE</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Both members confirming</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2728,27 +2592,27 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Mahesh Rajendra completes docs/team/PEER_REVIEW.md and the reviewer notes in this workbook, then sets review status to REVIEWED</t>
+          <t>Re-run python scripts/verify_signatures.py before the final push</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Internal review evidence. Not a substitute for the official review.</t>
+          <t>Confirms no signed document changed since it was signed. Typed confirmations are not cryptographic, so the content hash is what makes a later edit detectable.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Mahesh Rajendra</t>
+          <t>Krishna Annavaram</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>PENDING REVIEWER CONFIRMATION</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Reviewer performing the review</t>
+          <t>Final code freeze</t>
         </is>
       </c>
     </row>
@@ -2758,27 +2622,27 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Official automated review against the Hackathon Rubric</t>
+          <t>Mahesh Rajendra completes docs/team/PEER_REVIEW.md and the reviewer notes in this workbook, then sets review status to REVIEWED</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>REQ-010. The team's own validation is not the evaluation the requirement describes.</t>
+          <t>Internal review evidence. Not a substitute for the official review.</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>External evaluator</t>
+          <t>Mahesh Rajendra</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>EXTERNAL - PENDING</t>
+          <t>PENDING REVIEWER CONFIRMATION</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>The evaluator running it</t>
+          <t>Reviewer performing the review</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2652,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Official per-team Excel review report produced by the reviewer</t>
+          <t>Official automated review against the Hackathon Rubric</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>REQ-012. This workbook is internal preparation and is not that report.</t>
+          <t>REQ-010. The team's own validation is not the evaluation the requirement describes.</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -2808,7 +2672,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>The evaluator producing it</t>
+          <t>The evaluator running it</t>
         </is>
       </c>
     </row>
@@ -2818,12 +2682,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Grade awarded and bands applied (Pass &gt;= 60, Not Yet Passed &lt; 60)</t>
+          <t>Official per-team Excel review report produced by the reviewer</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>REQ-013. The bands are recorded here; whether they were applied is the evaluator's fact.</t>
+          <t>REQ-012. This workbook is internal preparation and is not that report.</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -2838,7 +2702,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>A grade being issued</t>
+          <t>The evaluator producing it</t>
         </is>
       </c>
     </row>
@@ -2848,27 +2712,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Re-run the Gemini judge (eval/requirements_judge.py) once API credits are restored</t>
+          <t>Grade awarded and bands applied (Pass &gt;= 60, Not Yet Passed &lt; 60)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Every Gemini model currently returns 402 RESOURCE_EXHAUSTED, so judged metrics are null rather than measured.</t>
+          <t>REQ-013. The bands are recorded here; whether they were applied is the evaluator's fact.</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Krishna Annavaram</t>
+          <t>External evaluator</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
+          <t>EXTERNAL - PENDING</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Google AI Studio prepayment credits</t>
+          <t>A grade being issued</t>
         </is>
       </c>
     </row>
@@ -2878,12 +2742,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Regenerate DeepEval judged metrics once credits are restored</t>
+          <t>Re-run the Gemini judge (eval/requirements_judge.py) once API credits are restored</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>reports/eval_report.json currently carries null judge_* metrics with the reason recorded. Deterministic metrics are unaffected.</t>
+          <t>Every Gemini model currently returns 402 RESOURCE_EXHAUSTED, so judged metrics are null rather than measured.</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -2908,12 +2772,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Re-run scripts/regenerate_evidence.py and the three verifier scripts before the final push</t>
+          <t>Regenerate DeepEval judged metrics once credits are restored</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Evidence freshness: committed measurements must come from the committed code state.</t>
+          <t>reports/eval_report.json currently carries null judge_* metrics with the reason recorded. Deterministic metrics are unaffected.</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -2923,12 +2787,12 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>NOT STARTED</t>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Final code freeze</t>
+          <t>Google AI Studio prepayment credits</t>
         </is>
       </c>
     </row>
@@ -2938,12 +2802,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Final secret scan and clean git status before the push</t>
+          <t>Re-run scripts/regenerate_evidence.py and the three verifier scripts before the final push</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>No .env, key, token, credential or PII may be committed.</t>
+          <t>Evidence freshness: committed measurements must come from the committed code state.</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -2968,27 +2832,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>REQ-035 - LangGraph MIT licence</t>
+          <t>Final secret scan and clean git status before the push</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Third-party licence evidence is now recorded in docs/THIRD_PARTY_LICENSES.md and reports/dependency_licenses.json. The source requires no licence artifact, so the check itself cannot pass.</t>
+          <t>No .env, key, token, credential or PII may be committed.</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>N/A - source specification gap</t>
+          <t>Krishna Annavaram</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>WILL NOT CLOSE</t>
+          <t>NOT STARTED</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>The source document</t>
+          <t>Final code freeze</t>
         </is>
       </c>
     </row>
@@ -2998,12 +2862,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>REQ-045 - numeric DTI threshold</t>
+          <t>REQ-035 - LangGraph MIT licence</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Thresholds are read from the retrieved, versioned policy corpus at runtime. The source document states no DTI figure.</t>
+          <t>Third-party licence evidence is now recorded in docs/THIRD_PARTY_LICENSES.md and reports/dependency_licenses.json. The source requires no licence artifact, so the check itself cannot pass.</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -3028,25 +2892,55 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
+          <t>REQ-045 - numeric DTI threshold</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Thresholds are read from the retrieved, versioned policy corpus at runtime. The source document states no DTI figure.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>N/A - source specification gap</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>WILL NOT CLOSE</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>The source document</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>REQ-046 - high-value monetary boundary</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>High-value routing keys off the policy corpus classification. The source document states no monetary boundary.</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>N/A - source specification gap</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>WILL NOT CLOSE</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>The source document</t>
         </is>
